--- a/v3/OG0044/OG0044_ReadingQuiz.xlsx
+++ b/v3/OG0044/OG0044_ReadingQuiz.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUIZ_LIST" sheetId="1" r:id="R736560e218d74343"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUESTIONS" sheetId="2" r:id="Rabc3cac88c944096"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANSWER_SCORING" sheetId="3" r:id="R520a7dbbc1b84019"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FEEDBACK" sheetId="4" r:id="Re448bc89952543eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUIZ_LIST" sheetId="1" r:id="R327d7b51fd1c4a4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUESTIONS" sheetId="2" r:id="R3c79023e42294970"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANSWER_SCORING" sheetId="3" r:id="R9d03bcf799134256"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FEEDBACK" sheetId="4" r:id="Raae49cec10f34ed3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -914,8 +914,8 @@
 who: the small kitten
 where: in Poco's bedroom
 where: at the window
-at_first: rest in the bedroom
-at_first: meet a small kitten</x:v>
+at_first: be in his bed
+at_first: hide under the bed</x:v>
       </x:c>
       <x:c r="K6" s="20" t="str">
         <x:v>who: poco_waggy / where: bedroom / at_first: resting</x:v>
@@ -994,12 +994,13 @@
         <x:v>SC06</x:v>
       </x:c>
       <x:c r="J8" s="20" t="str">
-        <x:v>his flashlight.
+        <x:v>flashlight.
+his
 Poco
 takes</x:v>
       </x:c>
       <x:c r="K8" s="20" t="str">
-        <x:v>Poco → takes → his flashlight.</x:v>
+        <x:v>Poco → takes → his → flashlight.</x:v>
       </x:c>
       <x:c r="L8" s="20" t="str">
         <x:v>exact -&gt; 100; LCS ratio &gt;= .75 -&gt; 67; LCS ratio &gt;= .40 -&gt; 33; otherwise -&gt; 0</x:v>
@@ -1076,8 +1077,8 @@
       </x:c>
       <x:c r="J10" s="20" t="str">
         <x:v>A. It is only a small kitten. [100]
-B. The visitor is smaller than I thought. [67]
-C. My dinosaur pajamas are at the window. [33]
+B. It is small. [67]
+C. It is my pajamas. [33]
 D. The room is empty. [0]</x:v>
       </x:c>
       <x:c r="K10" s="20" t="str">
@@ -1622,7 +1623,7 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="D17" s="30" t="str">
-        <x:v>Poco → takes → his flashlight.</x:v>
+        <x:v>Poco → takes → his → flashlight.</x:v>
       </x:c>
       <x:c r="E17" s="30" t="str">
         <x:v>Correct</x:v>
@@ -1657,7 +1658,7 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="D18" s="32" t="str">
-        <x:v>Poco → takes → his flashlight.</x:v>
+        <x:v>Poco → takes → his → flashlight.</x:v>
       </x:c>
       <x:c r="E18" s="32" t="str">
         <x:v>Constructed response</x:v>
@@ -1692,7 +1693,7 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="D19" s="34" t="str">
-        <x:v>Poco → takes → his flashlight.</x:v>
+        <x:v>Poco → takes → his → flashlight.</x:v>
       </x:c>
       <x:c r="E19" s="34" t="str">
         <x:v>Constructed response</x:v>
@@ -1727,7 +1728,7 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="D20" s="36" t="str">
-        <x:v>Poco → takes → his flashlight.</x:v>
+        <x:v>Poco → takes → his → flashlight.</x:v>
       </x:c>
       <x:c r="E20" s="36" t="str">
         <x:v>Constructed response</x:v>
@@ -1937,7 +1938,7 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="D26" s="32" t="str">
-        <x:v>The visitor is smaller than I thought.</x:v>
+        <x:v>It is small.</x:v>
       </x:c>
       <x:c r="E26" s="32" t="str">
         <x:v>Distractor</x:v>
@@ -1952,7 +1953,7 @@
         <x:v>partial_internal_inference</x:v>
       </x:c>
       <x:c r="I26" s="32" t="str">
-        <x:v>위협이 줄었다는 변화는 이해했지만 방문자의 정체를 완전히 연결하지 못합니다.</x:v>
+        <x:v>방문자가 작다는 단서는 이해했지만 작은 동물이 kitten이라는 정체까지 연결하지 못합니다.</x:v>
       </x:c>
       <x:c r="J26" s="32" t="str">
         <x:v>핵심 생각은 잡았으므로 장면 근거와 더 정확히 연결합니다.</x:v>
@@ -1972,7 +1973,7 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="D27" s="34" t="str">
-        <x:v>My dinosaur pajamas are at the window.</x:v>
+        <x:v>It is my pajamas.</x:v>
       </x:c>
       <x:c r="E27" s="34" t="str">
         <x:v>Distractor</x:v>
